--- a/GDD/GDD_Appendix_No.2_Items.xlsx
+++ b/GDD/GDD_Appendix_No.2_Items.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="27932"/>
   <workbookPr filterPrivacy="1" defaultThemeVersion="124226"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{476B2A78-C848-4B28-9A30-81BA739C195A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C6806715-E175-4396-B730-D73724F16EDA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" tabRatio="853" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2565" uniqueCount="887">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2588" uniqueCount="889">
   <si>
     <t>название</t>
   </si>
@@ -2709,6 +2709,12 @@
   </si>
   <si>
     <t>multiple</t>
+  </si>
+  <si>
+    <t>6</t>
+  </si>
+  <si>
+    <t>0,001</t>
   </si>
 </sst>
 </file>
@@ -3188,7 +3194,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="172">
+  <cellXfs count="173">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3635,6 +3641,12 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="26" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3660,9 +3672,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="11" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="29" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -3692,7 +3701,7 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="49" fontId="5" fillId="4" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -6070,33 +6079,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="6" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="170" t="s">
         <v>30</v>
       </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
-      <c r="H1" s="169"/>
-      <c r="I1" s="169"/>
-      <c r="J1" s="169"/>
-      <c r="K1" s="169"/>
-      <c r="L1" s="169"/>
-      <c r="M1" s="169"/>
-      <c r="N1" s="169"/>
-      <c r="O1" s="169"/>
-      <c r="P1" s="169"/>
-      <c r="Q1" s="169"/>
-      <c r="R1" s="169"/>
-      <c r="S1" s="169"/>
-      <c r="T1" s="169"/>
-      <c r="U1" s="169"/>
-      <c r="V1" s="169"/>
-      <c r="W1" s="169"/>
-      <c r="X1" s="169"/>
-      <c r="Y1" s="169"/>
+      <c r="B1" s="170"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="170"/>
+      <c r="G1" s="170"/>
+      <c r="H1" s="170"/>
+      <c r="I1" s="170"/>
+      <c r="J1" s="170"/>
+      <c r="K1" s="170"/>
+      <c r="L1" s="170"/>
+      <c r="M1" s="170"/>
+      <c r="N1" s="170"/>
+      <c r="O1" s="170"/>
+      <c r="P1" s="170"/>
+      <c r="Q1" s="170"/>
+      <c r="R1" s="170"/>
+      <c r="S1" s="170"/>
+      <c r="T1" s="170"/>
+      <c r="U1" s="170"/>
+      <c r="V1" s="170"/>
+      <c r="W1" s="170"/>
+      <c r="X1" s="170"/>
+      <c r="Y1" s="170"/>
     </row>
     <row r="2" spans="1:42" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -6576,33 +6585,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="6" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="170" t="s">
         <v>31</v>
       </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
-      <c r="H1" s="169"/>
-      <c r="I1" s="169"/>
-      <c r="J1" s="169"/>
-      <c r="K1" s="169"/>
-      <c r="L1" s="169"/>
-      <c r="M1" s="169"/>
-      <c r="N1" s="169"/>
-      <c r="O1" s="169"/>
-      <c r="P1" s="169"/>
-      <c r="Q1" s="169"/>
-      <c r="R1" s="169"/>
-      <c r="S1" s="169"/>
-      <c r="T1" s="169"/>
-      <c r="U1" s="169"/>
-      <c r="V1" s="169"/>
-      <c r="W1" s="169"/>
-      <c r="X1" s="169"/>
-      <c r="Y1" s="169"/>
+      <c r="B1" s="170"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="170"/>
+      <c r="G1" s="170"/>
+      <c r="H1" s="170"/>
+      <c r="I1" s="170"/>
+      <c r="J1" s="170"/>
+      <c r="K1" s="170"/>
+      <c r="L1" s="170"/>
+      <c r="M1" s="170"/>
+      <c r="N1" s="170"/>
+      <c r="O1" s="170"/>
+      <c r="P1" s="170"/>
+      <c r="Q1" s="170"/>
+      <c r="R1" s="170"/>
+      <c r="S1" s="170"/>
+      <c r="T1" s="170"/>
+      <c r="U1" s="170"/>
+      <c r="V1" s="170"/>
+      <c r="W1" s="170"/>
+      <c r="X1" s="170"/>
+      <c r="Y1" s="170"/>
     </row>
     <row r="2" spans="1:42" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -8291,33 +8300,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="12" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="171" t="s">
         <v>327</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="170"/>
-      <c r="I1" s="170"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="170"/>
-      <c r="L1" s="170"/>
-      <c r="M1" s="170"/>
-      <c r="N1" s="170"/>
-      <c r="O1" s="170"/>
-      <c r="P1" s="170"/>
-      <c r="Q1" s="170"/>
-      <c r="R1" s="170"/>
-      <c r="S1" s="170"/>
-      <c r="T1" s="170"/>
-      <c r="U1" s="170"/>
-      <c r="V1" s="170"/>
-      <c r="W1" s="170"/>
-      <c r="X1" s="170"/>
-      <c r="Y1" s="170"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
+      <c r="O1" s="171"/>
+      <c r="P1" s="171"/>
+      <c r="Q1" s="171"/>
+      <c r="R1" s="171"/>
+      <c r="S1" s="171"/>
+      <c r="T1" s="171"/>
+      <c r="U1" s="171"/>
+      <c r="V1" s="171"/>
+      <c r="W1" s="171"/>
+      <c r="X1" s="171"/>
+      <c r="Y1" s="171"/>
     </row>
     <row r="2" spans="1:42" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
@@ -10653,33 +10662,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="12" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="171" t="s">
         <v>327</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="170"/>
-      <c r="I1" s="170"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="170"/>
-      <c r="L1" s="170"/>
-      <c r="M1" s="170"/>
-      <c r="N1" s="170"/>
-      <c r="O1" s="170"/>
-      <c r="P1" s="170"/>
-      <c r="Q1" s="170"/>
-      <c r="R1" s="170"/>
-      <c r="S1" s="170"/>
-      <c r="T1" s="170"/>
-      <c r="U1" s="170"/>
-      <c r="V1" s="170"/>
-      <c r="W1" s="170"/>
-      <c r="X1" s="170"/>
-      <c r="Y1" s="170"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
+      <c r="O1" s="171"/>
+      <c r="P1" s="171"/>
+      <c r="Q1" s="171"/>
+      <c r="R1" s="171"/>
+      <c r="S1" s="171"/>
+      <c r="T1" s="171"/>
+      <c r="U1" s="171"/>
+      <c r="V1" s="171"/>
+      <c r="W1" s="171"/>
+      <c r="X1" s="171"/>
+      <c r="Y1" s="171"/>
     </row>
     <row r="2" spans="1:42" s="12" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="18" t="s">
@@ -12398,33 +12407,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="171" t="s">
         <v>325</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="170"/>
-      <c r="I1" s="170"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="170"/>
-      <c r="L1" s="170"/>
-      <c r="M1" s="170"/>
-      <c r="N1" s="170"/>
-      <c r="O1" s="170"/>
-      <c r="P1" s="170"/>
-      <c r="Q1" s="170"/>
-      <c r="R1" s="170"/>
-      <c r="S1" s="170"/>
-      <c r="T1" s="170"/>
-      <c r="U1" s="170"/>
-      <c r="V1" s="170"/>
-      <c r="W1" s="170"/>
-      <c r="X1" s="170"/>
-      <c r="Y1" s="170"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
+      <c r="O1" s="171"/>
+      <c r="P1" s="171"/>
+      <c r="Q1" s="171"/>
+      <c r="R1" s="171"/>
+      <c r="S1" s="171"/>
+      <c r="T1" s="171"/>
+      <c r="U1" s="171"/>
+      <c r="V1" s="171"/>
+      <c r="W1" s="171"/>
+      <c r="X1" s="171"/>
+      <c r="Y1" s="171"/>
     </row>
     <row r="2" spans="1:42" ht="75" x14ac:dyDescent="0.25">
       <c r="A2" s="16" t="s">
@@ -12906,33 +12915,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="4" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="170" t="s">
+      <c r="A1" s="171" t="s">
         <v>326</v>
       </c>
-      <c r="B1" s="170"/>
-      <c r="C1" s="170"/>
-      <c r="D1" s="170"/>
-      <c r="E1" s="170"/>
-      <c r="F1" s="170"/>
-      <c r="G1" s="170"/>
-      <c r="H1" s="170"/>
-      <c r="I1" s="170"/>
-      <c r="J1" s="170"/>
-      <c r="K1" s="170"/>
-      <c r="L1" s="170"/>
-      <c r="M1" s="170"/>
-      <c r="N1" s="170"/>
-      <c r="O1" s="170"/>
-      <c r="P1" s="170"/>
-      <c r="Q1" s="170"/>
-      <c r="R1" s="170"/>
-      <c r="S1" s="170"/>
-      <c r="T1" s="170"/>
-      <c r="U1" s="170"/>
-      <c r="V1" s="170"/>
-      <c r="W1" s="170"/>
-      <c r="X1" s="170"/>
-      <c r="Y1" s="170"/>
+      <c r="B1" s="171"/>
+      <c r="C1" s="171"/>
+      <c r="D1" s="171"/>
+      <c r="E1" s="171"/>
+      <c r="F1" s="171"/>
+      <c r="G1" s="171"/>
+      <c r="H1" s="171"/>
+      <c r="I1" s="171"/>
+      <c r="J1" s="171"/>
+      <c r="K1" s="171"/>
+      <c r="L1" s="171"/>
+      <c r="M1" s="171"/>
+      <c r="N1" s="171"/>
+      <c r="O1" s="171"/>
+      <c r="P1" s="171"/>
+      <c r="Q1" s="171"/>
+      <c r="R1" s="171"/>
+      <c r="S1" s="171"/>
+      <c r="T1" s="171"/>
+      <c r="U1" s="171"/>
+      <c r="V1" s="171"/>
+      <c r="W1" s="171"/>
+      <c r="X1" s="171"/>
+      <c r="Y1" s="171"/>
     </row>
     <row r="2" spans="1:42" s="4" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="3" t="s">
@@ -14583,23 +14592,23 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="168" t="s">
+      <c r="A1" s="169" t="s">
         <v>475</v>
       </c>
-      <c r="B1" s="168" t="s">
+      <c r="B1" s="169" t="s">
         <v>474</v>
       </c>
-      <c r="C1" s="168" t="s">
+      <c r="C1" s="169" t="s">
         <v>485</v>
       </c>
-      <c r="D1" s="168"/>
-      <c r="E1" s="168"/>
-      <c r="F1" s="168"/>
-      <c r="G1" s="168"/>
+      <c r="D1" s="169"/>
+      <c r="E1" s="169"/>
+      <c r="F1" s="169"/>
+      <c r="G1" s="169"/>
     </row>
     <row r="2" spans="1:7" ht="23.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="168"/>
-      <c r="B2" s="168"/>
+      <c r="A2" s="169"/>
+      <c r="B2" s="169"/>
       <c r="C2" s="17" t="s">
         <v>473</v>
       </c>
@@ -15721,11 +15730,11 @@
       <c r="I13" s="68">
         <v>0.75</v>
       </c>
-      <c r="J13" s="161" t="s">
+      <c r="J13" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="K13" s="161"/>
-      <c r="L13" s="161"/>
+      <c r="K13" s="153"/>
+      <c r="L13" s="153"/>
       <c r="M13" s="45"/>
       <c r="N13" s="45"/>
       <c r="O13" s="45"/>
@@ -15769,11 +15778,11 @@
       <c r="I14" s="48">
         <v>0.5</v>
       </c>
-      <c r="J14" s="161" t="s">
+      <c r="J14" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="K14" s="161"/>
-      <c r="L14" s="161"/>
+      <c r="K14" s="153"/>
+      <c r="L14" s="153"/>
       <c r="M14" s="24"/>
       <c r="N14" s="24"/>
       <c r="O14" s="24"/>
@@ -15817,11 +15826,11 @@
       <c r="I15" s="53">
         <v>0.25</v>
       </c>
-      <c r="J15" s="161" t="s">
+      <c r="J15" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="K15" s="161"/>
-      <c r="L15" s="161"/>
+      <c r="K15" s="153"/>
+      <c r="L15" s="153"/>
       <c r="M15" s="60"/>
       <c r="N15" s="60"/>
       <c r="O15" s="60"/>
@@ -15847,21 +15856,21 @@
       <c r="C16" s="40" t="s">
         <v>441</v>
       </c>
-      <c r="D16" s="152" t="s">
+      <c r="D16" s="154" t="s">
         <v>442</v>
       </c>
-      <c r="E16" s="153"/>
-      <c r="F16" s="153"/>
-      <c r="G16" s="153"/>
-      <c r="H16" s="154"/>
+      <c r="E16" s="155"/>
+      <c r="F16" s="155"/>
+      <c r="G16" s="155"/>
+      <c r="H16" s="156"/>
       <c r="I16" s="50">
         <v>0</v>
       </c>
-      <c r="J16" s="161" t="s">
+      <c r="J16" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="K16" s="161"/>
-      <c r="L16" s="161"/>
+      <c r="K16" s="153"/>
+      <c r="L16" s="153"/>
       <c r="M16" s="40"/>
       <c r="N16" s="40"/>
       <c r="O16" s="40"/>
@@ -15887,21 +15896,21 @@
       <c r="C17" s="24" t="s">
         <v>441</v>
       </c>
-      <c r="D17" s="158" t="s">
+      <c r="D17" s="160" t="s">
         <v>442</v>
       </c>
-      <c r="E17" s="159"/>
-      <c r="F17" s="159"/>
-      <c r="G17" s="159"/>
-      <c r="H17" s="160"/>
+      <c r="E17" s="161"/>
+      <c r="F17" s="161"/>
+      <c r="G17" s="161"/>
+      <c r="H17" s="162"/>
       <c r="I17" s="48">
         <v>0</v>
       </c>
-      <c r="J17" s="161" t="s">
+      <c r="J17" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="K17" s="161"/>
-      <c r="L17" s="161"/>
+      <c r="K17" s="153"/>
+      <c r="L17" s="153"/>
       <c r="M17" s="24"/>
       <c r="N17" s="24"/>
       <c r="O17" s="24"/>
@@ -15927,21 +15936,21 @@
       <c r="C18" s="24" t="s">
         <v>441</v>
       </c>
-      <c r="D18" s="158" t="s">
+      <c r="D18" s="160" t="s">
         <v>442</v>
       </c>
-      <c r="E18" s="159"/>
-      <c r="F18" s="159"/>
-      <c r="G18" s="159"/>
-      <c r="H18" s="160"/>
+      <c r="E18" s="161"/>
+      <c r="F18" s="161"/>
+      <c r="G18" s="161"/>
+      <c r="H18" s="162"/>
       <c r="I18" s="48">
         <v>0</v>
       </c>
-      <c r="J18" s="161" t="s">
+      <c r="J18" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="K18" s="161"/>
-      <c r="L18" s="161"/>
+      <c r="K18" s="153"/>
+      <c r="L18" s="153"/>
       <c r="M18" s="24"/>
       <c r="N18" s="24"/>
       <c r="O18" s="24"/>
@@ -15967,21 +15976,21 @@
       <c r="C19" s="39" t="s">
         <v>444</v>
       </c>
-      <c r="D19" s="155" t="s">
+      <c r="D19" s="157" t="s">
         <v>445</v>
       </c>
-      <c r="E19" s="156"/>
-      <c r="F19" s="156"/>
-      <c r="G19" s="156"/>
-      <c r="H19" s="157"/>
+      <c r="E19" s="158"/>
+      <c r="F19" s="158"/>
+      <c r="G19" s="158"/>
+      <c r="H19" s="159"/>
       <c r="I19" s="77">
         <v>0</v>
       </c>
-      <c r="J19" s="161" t="s">
+      <c r="J19" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="K19" s="161"/>
-      <c r="L19" s="161"/>
+      <c r="K19" s="153"/>
+      <c r="L19" s="153"/>
       <c r="M19" s="39"/>
       <c r="N19" s="39"/>
       <c r="O19" s="39"/>
@@ -16007,13 +16016,13 @@
       <c r="C20" s="45" t="s">
         <v>447</v>
       </c>
-      <c r="D20" s="152" t="s">
+      <c r="D20" s="154" t="s">
         <v>718</v>
       </c>
-      <c r="E20" s="153"/>
-      <c r="F20" s="153"/>
-      <c r="G20" s="153"/>
-      <c r="H20" s="154"/>
+      <c r="E20" s="155"/>
+      <c r="F20" s="155"/>
+      <c r="G20" s="155"/>
+      <c r="H20" s="156"/>
       <c r="I20" s="68">
         <v>0</v>
       </c>
@@ -16063,13 +16072,13 @@
       <c r="C21" s="52" t="s">
         <v>449</v>
       </c>
-      <c r="D21" s="155" t="s">
+      <c r="D21" s="157" t="s">
         <v>718</v>
       </c>
-      <c r="E21" s="156"/>
-      <c r="F21" s="156"/>
-      <c r="G21" s="156"/>
-      <c r="H21" s="157"/>
+      <c r="E21" s="158"/>
+      <c r="F21" s="158"/>
+      <c r="G21" s="158"/>
+      <c r="H21" s="159"/>
       <c r="I21" s="53">
         <v>0</v>
       </c>
@@ -16419,19 +16428,19 @@
     </row>
   </sheetData>
   <mergeCells count="13">
-    <mergeCell ref="J13:L13"/>
-    <mergeCell ref="J14:L14"/>
-    <mergeCell ref="J15:L15"/>
-    <mergeCell ref="J16:L16"/>
-    <mergeCell ref="J17:L17"/>
+    <mergeCell ref="J18:L18"/>
+    <mergeCell ref="J19:L19"/>
     <mergeCell ref="D20:H20"/>
     <mergeCell ref="D21:H21"/>
     <mergeCell ref="D16:H16"/>
     <mergeCell ref="D17:H17"/>
     <mergeCell ref="D18:H18"/>
     <mergeCell ref="D19:H19"/>
-    <mergeCell ref="J18:L18"/>
-    <mergeCell ref="J19:L19"/>
+    <mergeCell ref="J13:L13"/>
+    <mergeCell ref="J14:L14"/>
+    <mergeCell ref="J15:L15"/>
+    <mergeCell ref="J16:L16"/>
+    <mergeCell ref="J17:L17"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18567,7 +18576,7 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:25" ht="49.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="145" t="s">
+      <c r="A1" s="172" t="s">
         <v>738</v>
       </c>
       <c r="B1" s="145" t="s">
@@ -18644,7 +18653,7 @@
       </c>
     </row>
     <row r="2" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="145">
+      <c r="A2" s="172">
         <v>1</v>
       </c>
       <c r="B2" s="145" t="s">
@@ -18695,7 +18704,7 @@
       <c r="Y2" s="145"/>
     </row>
     <row r="3" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="145">
+      <c r="A3" s="172">
         <v>2</v>
       </c>
       <c r="B3" s="145" t="s">
@@ -18746,7 +18755,7 @@
       <c r="Y3" s="145"/>
     </row>
     <row r="4" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="145">
+      <c r="A4" s="172">
         <v>3</v>
       </c>
       <c r="B4" s="145" t="s">
@@ -18797,7 +18806,7 @@
       <c r="Y4" s="145"/>
     </row>
     <row r="5" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="145">
+      <c r="A5" s="172">
         <v>4</v>
       </c>
       <c r="B5" s="145" t="s">
@@ -18848,7 +18857,7 @@
       <c r="Y5" s="145"/>
     </row>
     <row r="6" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="145">
+      <c r="A6" s="172">
         <v>5</v>
       </c>
       <c r="B6" s="145" t="s">
@@ -18870,11 +18879,11 @@
         <v>0.75</v>
       </c>
       <c r="H6" s="145"/>
-      <c r="I6" s="165" t="s">
+      <c r="I6" s="166" t="s">
         <v>842</v>
       </c>
-      <c r="J6" s="166"/>
-      <c r="K6" s="167"/>
+      <c r="J6" s="167"/>
+      <c r="K6" s="168"/>
       <c r="L6" s="145"/>
       <c r="M6" s="145"/>
       <c r="N6" s="145"/>
@@ -18891,7 +18900,7 @@
       <c r="Y6" s="145"/>
     </row>
     <row r="7" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="145">
+      <c r="A7" s="172">
         <v>6</v>
       </c>
       <c r="B7" s="145" t="s">
@@ -18913,11 +18922,11 @@
         <v>0.75</v>
       </c>
       <c r="H7" s="145"/>
-      <c r="I7" s="165" t="s">
+      <c r="I7" s="166" t="s">
         <v>842</v>
       </c>
-      <c r="J7" s="166"/>
-      <c r="K7" s="167"/>
+      <c r="J7" s="167"/>
+      <c r="K7" s="168"/>
       <c r="L7" s="145"/>
       <c r="M7" s="145"/>
       <c r="N7" s="145"/>
@@ -18934,7 +18943,7 @@
       <c r="Y7" s="145"/>
     </row>
     <row r="8" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="145">
+      <c r="A8" s="172">
         <v>7</v>
       </c>
       <c r="B8" s="145" t="s">
@@ -18956,11 +18965,11 @@
         <v>0.5</v>
       </c>
       <c r="H8" s="145"/>
-      <c r="I8" s="165" t="s">
+      <c r="I8" s="166" t="s">
         <v>842</v>
       </c>
-      <c r="J8" s="166"/>
-      <c r="K8" s="167"/>
+      <c r="J8" s="167"/>
+      <c r="K8" s="168"/>
       <c r="L8" s="145"/>
       <c r="M8" s="145"/>
       <c r="N8" s="145"/>
@@ -18977,7 +18986,7 @@
       <c r="Y8" s="145"/>
     </row>
     <row r="9" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A9" s="145">
+      <c r="A9" s="172">
         <v>8</v>
       </c>
       <c r="B9" s="145" t="s">
@@ -18999,11 +19008,11 @@
         <v>0.5</v>
       </c>
       <c r="H9" s="145"/>
-      <c r="I9" s="165" t="s">
+      <c r="I9" s="166" t="s">
         <v>842</v>
       </c>
-      <c r="J9" s="166"/>
-      <c r="K9" s="167"/>
+      <c r="J9" s="167"/>
+      <c r="K9" s="168"/>
       <c r="L9" s="145"/>
       <c r="M9" s="145"/>
       <c r="N9" s="145"/>
@@ -19020,7 +19029,7 @@
       <c r="Y9" s="145"/>
     </row>
     <row r="10" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="145">
+      <c r="A10" s="172">
         <v>9</v>
       </c>
       <c r="B10" s="145" t="s">
@@ -19075,7 +19084,7 @@
       <c r="Y10" s="145"/>
     </row>
     <row r="11" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="145">
+      <c r="A11" s="172">
         <v>10</v>
       </c>
       <c r="B11" s="145" t="s">
@@ -19130,7 +19139,7 @@
       <c r="Y11" s="145"/>
     </row>
     <row r="12" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="145">
+      <c r="A12" s="172">
         <v>11</v>
       </c>
       <c r="B12" s="145" t="s">
@@ -19185,7 +19194,7 @@
       <c r="Y12" s="145"/>
     </row>
     <row r="13" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="145">
+      <c r="A13" s="172">
         <v>12</v>
       </c>
       <c r="B13" s="145" t="s">
@@ -19240,7 +19249,7 @@
       <c r="Y13" s="145"/>
     </row>
     <row r="14" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="145">
+      <c r="A14" s="172">
         <v>13</v>
       </c>
       <c r="B14" s="145" t="s">
@@ -19269,7 +19278,7 @@
         <v>1</v>
       </c>
       <c r="K14" s="145" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="L14" s="145" t="s">
         <v>745</v>
@@ -19307,7 +19316,7 @@
       <c r="Y14" s="145"/>
     </row>
     <row r="15" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="145">
+      <c r="A15" s="172">
         <v>14</v>
       </c>
       <c r="B15" s="145" t="s">
@@ -19336,7 +19345,7 @@
         <v>1</v>
       </c>
       <c r="K15" s="145" t="s">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="L15" s="145" t="s">
         <v>756</v>
@@ -19378,7 +19387,7 @@
       <c r="Y15" s="145"/>
     </row>
     <row r="16" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A16" s="145">
+      <c r="A16" s="172">
         <v>15</v>
       </c>
       <c r="B16" s="145" t="s">
@@ -19400,11 +19409,11 @@
         <v>0.1</v>
       </c>
       <c r="H16" s="145"/>
-      <c r="I16" s="161" t="s">
+      <c r="I16" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J16" s="161"/>
-      <c r="K16" s="161"/>
+      <c r="J16" s="153"/>
+      <c r="K16" s="153"/>
       <c r="L16" s="145"/>
       <c r="M16" s="145"/>
       <c r="N16" s="145"/>
@@ -19421,7 +19430,7 @@
       <c r="Y16" s="145"/>
     </row>
     <row r="17" spans="1:28" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A17" s="145">
+      <c r="A17" s="172">
         <v>16</v>
       </c>
       <c r="B17" s="145" t="s">
@@ -19443,11 +19452,11 @@
         <v>0.1</v>
       </c>
       <c r="H17" s="145"/>
-      <c r="I17" s="161" t="s">
+      <c r="I17" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J17" s="161"/>
-      <c r="K17" s="161"/>
+      <c r="J17" s="153"/>
+      <c r="K17" s="153"/>
       <c r="L17" s="145"/>
       <c r="M17" s="145"/>
       <c r="N17" s="145"/>
@@ -19464,7 +19473,7 @@
       <c r="Y17" s="145"/>
     </row>
     <row r="18" spans="1:28" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A18" s="145">
+      <c r="A18" s="172">
         <v>17</v>
       </c>
       <c r="B18" s="145" t="s">
@@ -19486,11 +19495,11 @@
         <v>0.1</v>
       </c>
       <c r="H18" s="145"/>
-      <c r="I18" s="161" t="s">
+      <c r="I18" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J18" s="161"/>
-      <c r="K18" s="161"/>
+      <c r="J18" s="153"/>
+      <c r="K18" s="153"/>
       <c r="L18" s="145"/>
       <c r="M18" s="145"/>
       <c r="N18" s="145"/>
@@ -19507,7 +19516,7 @@
       <c r="Y18" s="145"/>
     </row>
     <row r="19" spans="1:28" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A19" s="145">
+      <c r="A19" s="172">
         <v>18</v>
       </c>
       <c r="B19" s="145" t="s">
@@ -19560,7 +19569,7 @@
       <c r="AB19" s="148"/>
     </row>
     <row r="20" spans="1:28" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A20" s="145">
+      <c r="A20" s="172">
         <v>19</v>
       </c>
       <c r="B20" s="145" t="s">
@@ -19613,7 +19622,7 @@
       <c r="AB20" s="148"/>
     </row>
     <row r="21" spans="1:28" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="145">
+      <c r="A21" s="172">
         <v>20</v>
       </c>
       <c r="B21" s="145" t="s">
@@ -19635,11 +19644,11 @@
         <v>0.75</v>
       </c>
       <c r="H21" s="145"/>
-      <c r="I21" s="161" t="s">
+      <c r="I21" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J21" s="161"/>
-      <c r="K21" s="161"/>
+      <c r="J21" s="153"/>
+      <c r="K21" s="153"/>
       <c r="L21" s="145"/>
       <c r="M21" s="145"/>
       <c r="N21" s="145"/>
@@ -19658,7 +19667,7 @@
       <c r="AB21" s="148"/>
     </row>
     <row r="22" spans="1:28" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="145">
+      <c r="A22" s="172">
         <v>21</v>
       </c>
       <c r="B22" s="145" t="s">
@@ -19680,11 +19689,11 @@
         <v>0.5</v>
       </c>
       <c r="H22" s="145"/>
-      <c r="I22" s="161" t="s">
+      <c r="I22" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J22" s="161"/>
-      <c r="K22" s="161"/>
+      <c r="J22" s="153"/>
+      <c r="K22" s="153"/>
       <c r="L22" s="145"/>
       <c r="M22" s="145"/>
       <c r="N22" s="145"/>
@@ -19703,7 +19712,7 @@
       <c r="AB22" s="148"/>
     </row>
     <row r="23" spans="1:28" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="145">
+      <c r="A23" s="172">
         <v>22</v>
       </c>
       <c r="B23" s="145" t="s">
@@ -19737,14 +19746,14 @@
       <c r="L23" s="145" t="s">
         <v>754</v>
       </c>
-      <c r="M23" s="145">
-        <v>1</v>
+      <c r="M23" s="145" t="s">
+        <v>693</v>
       </c>
       <c r="N23" s="145" t="s">
         <v>758</v>
       </c>
-      <c r="O23" s="145">
-        <v>2</v>
+      <c r="O23" s="145" t="s">
+        <v>691</v>
       </c>
       <c r="P23" s="145" t="s">
         <v>670</v>
@@ -19768,7 +19777,7 @@
       <c r="AB23" s="148"/>
     </row>
     <row r="24" spans="1:28" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A24" s="145">
+      <c r="A24" s="172">
         <v>23</v>
       </c>
       <c r="B24" s="145" t="s">
@@ -19802,8 +19811,8 @@
       <c r="L24" s="145" t="s">
         <v>754</v>
       </c>
-      <c r="M24" s="145">
-        <v>1</v>
+      <c r="M24" s="145" t="s">
+        <v>693</v>
       </c>
       <c r="N24" s="145" t="s">
         <v>840</v>
@@ -19833,7 +19842,7 @@
       <c r="AB24" s="148"/>
     </row>
     <row r="25" spans="1:28" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="145">
+      <c r="A25" s="172">
         <v>24</v>
       </c>
       <c r="B25" s="145" t="s">
@@ -19867,17 +19876,21 @@
       <c r="L25" s="145" t="s">
         <v>754</v>
       </c>
-      <c r="M25" s="145">
-        <v>1</v>
+      <c r="M25" s="145" t="s">
+        <v>693</v>
       </c>
       <c r="N25" s="145" t="s">
         <v>760</v>
       </c>
-      <c r="O25" s="145"/>
+      <c r="O25" s="145" t="s">
+        <v>691</v>
+      </c>
       <c r="P25" s="145" t="s">
         <v>672</v>
       </c>
-      <c r="Q25" s="145"/>
+      <c r="Q25" s="145" t="s">
+        <v>691</v>
+      </c>
       <c r="R25" s="145" t="s">
         <v>678</v>
       </c>
@@ -19892,7 +19905,7 @@
       <c r="Y25" s="145"/>
     </row>
     <row r="26" spans="1:28" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="145">
+      <c r="A26" s="172">
         <v>25</v>
       </c>
       <c r="B26" s="145" t="s">
@@ -19932,8 +19945,8 @@
       <c r="N26" s="145" t="s">
         <v>747</v>
       </c>
-      <c r="O26" s="145">
-        <v>3</v>
+      <c r="O26" s="145" t="s">
+        <v>887</v>
       </c>
       <c r="P26" s="145"/>
       <c r="Q26" s="145"/>
@@ -19947,7 +19960,7 @@
       <c r="Y26" s="145"/>
     </row>
     <row r="27" spans="1:28" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="145">
+      <c r="A27" s="172">
         <v>26</v>
       </c>
       <c r="B27" s="145" t="s">
@@ -19987,8 +20000,8 @@
       <c r="N27" s="145" t="s">
         <v>748</v>
       </c>
-      <c r="O27" s="145">
-        <v>3</v>
+      <c r="O27" s="145" t="s">
+        <v>845</v>
       </c>
       <c r="P27" s="145"/>
       <c r="Q27" s="145"/>
@@ -20002,7 +20015,7 @@
       <c r="Y27" s="145"/>
     </row>
     <row r="28" spans="1:28" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="145">
+      <c r="A28" s="172">
         <v>27</v>
       </c>
       <c r="B28" s="145" t="s">
@@ -20042,8 +20055,8 @@
       <c r="N28" s="145" t="s">
         <v>749</v>
       </c>
-      <c r="O28" s="145">
-        <v>3</v>
+      <c r="O28" s="145" t="s">
+        <v>844</v>
       </c>
       <c r="P28" s="145"/>
       <c r="Q28" s="145"/>
@@ -20057,7 +20070,7 @@
       <c r="Y28" s="145"/>
     </row>
     <row r="29" spans="1:28" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="145">
+      <c r="A29" s="172">
         <v>28</v>
       </c>
       <c r="B29" s="145" t="s">
@@ -20097,8 +20110,8 @@
       <c r="N29" s="145" t="s">
         <v>747</v>
       </c>
-      <c r="O29" s="145">
-        <v>2</v>
+      <c r="O29" s="145" t="s">
+        <v>887</v>
       </c>
       <c r="P29" s="145"/>
       <c r="Q29" s="145"/>
@@ -20112,7 +20125,7 @@
       <c r="Y29" s="145"/>
     </row>
     <row r="30" spans="1:28" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A30" s="145">
+      <c r="A30" s="172">
         <v>29</v>
       </c>
       <c r="B30" s="145" t="s">
@@ -20152,8 +20165,8 @@
       <c r="N30" s="145" t="s">
         <v>748</v>
       </c>
-      <c r="O30" s="145">
-        <v>2</v>
+      <c r="O30" s="145" t="s">
+        <v>845</v>
       </c>
       <c r="P30" s="145"/>
       <c r="Q30" s="145"/>
@@ -20167,7 +20180,7 @@
       <c r="Y30" s="145"/>
     </row>
     <row r="31" spans="1:28" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="145">
+      <c r="A31" s="172">
         <v>30</v>
       </c>
       <c r="B31" s="145" t="s">
@@ -20222,7 +20235,7 @@
       <c r="Y31" s="139"/>
     </row>
     <row r="32" spans="1:28" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="145">
+      <c r="A32" s="172">
         <v>31</v>
       </c>
       <c r="B32" s="145" t="s">
@@ -20247,8 +20260,8 @@
       <c r="I32" s="33" t="s">
         <v>773</v>
       </c>
-      <c r="J32" s="33">
-        <v>1</v>
+      <c r="J32" s="33" t="s">
+        <v>844</v>
       </c>
       <c r="K32" s="33" t="s">
         <v>686</v>
@@ -20260,9 +20273,7 @@
         <v>1</v>
       </c>
       <c r="N32" s="145"/>
-      <c r="O32" s="33" t="s">
-        <v>691</v>
-      </c>
+      <c r="O32" s="33"/>
       <c r="P32" s="145"/>
       <c r="Q32" s="145"/>
       <c r="R32" s="145"/>
@@ -20275,7 +20286,7 @@
       <c r="Y32" s="145"/>
     </row>
     <row r="33" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A33" s="145">
+      <c r="A33" s="172">
         <v>32</v>
       </c>
       <c r="B33" s="145" t="s">
@@ -20300,8 +20311,8 @@
       <c r="I33" s="33" t="s">
         <v>773</v>
       </c>
-      <c r="J33" s="33">
-        <v>1</v>
+      <c r="J33" s="33" t="s">
+        <v>844</v>
       </c>
       <c r="K33" s="33" t="s">
         <v>686</v>
@@ -20330,7 +20341,7 @@
       <c r="Y33" s="145"/>
     </row>
     <row r="34" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A34" s="145">
+      <c r="A34" s="172">
         <v>33</v>
       </c>
       <c r="B34" s="145" t="s">
@@ -20355,8 +20366,8 @@
       <c r="I34" s="33" t="s">
         <v>773</v>
       </c>
-      <c r="J34" s="33">
-        <v>1</v>
+      <c r="J34" s="33" t="s">
+        <v>844</v>
       </c>
       <c r="K34" s="33" t="s">
         <v>686</v>
@@ -20385,7 +20396,7 @@
       <c r="Y34" s="145"/>
     </row>
     <row r="35" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A35" s="145">
+      <c r="A35" s="172">
         <v>34</v>
       </c>
       <c r="B35" s="145" t="s">
@@ -20410,8 +20421,8 @@
       <c r="I35" s="33" t="s">
         <v>773</v>
       </c>
-      <c r="J35" s="33">
-        <v>1</v>
+      <c r="J35" s="33" t="s">
+        <v>844</v>
       </c>
       <c r="K35" s="33" t="s">
         <v>686</v>
@@ -20440,7 +20451,7 @@
       <c r="Y35" s="145"/>
     </row>
     <row r="36" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A36" s="145">
+      <c r="A36" s="172">
         <v>35</v>
       </c>
       <c r="B36" s="145" t="s">
@@ -20465,8 +20476,8 @@
       <c r="I36" s="33" t="s">
         <v>773</v>
       </c>
-      <c r="J36" s="33">
-        <v>1</v>
+      <c r="J36" s="33" t="s">
+        <v>844</v>
       </c>
       <c r="K36" s="33" t="s">
         <v>686</v>
@@ -20495,7 +20506,7 @@
       <c r="Y36" s="145"/>
     </row>
     <row r="37" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A37" s="145">
+      <c r="A37" s="172">
         <v>36</v>
       </c>
       <c r="B37" s="145" t="s">
@@ -20520,8 +20531,8 @@
       <c r="I37" s="33" t="s">
         <v>773</v>
       </c>
-      <c r="J37" s="33">
-        <v>1</v>
+      <c r="J37" s="33" t="s">
+        <v>844</v>
       </c>
       <c r="K37" s="33" t="s">
         <v>686</v>
@@ -20550,7 +20561,7 @@
       <c r="Y37" s="145"/>
     </row>
     <row r="38" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A38" s="145">
+      <c r="A38" s="172">
         <v>37</v>
       </c>
       <c r="B38" s="145" t="s">
@@ -20572,11 +20583,11 @@
         <v>1</v>
       </c>
       <c r="H38" s="140"/>
-      <c r="I38" s="165" t="s">
+      <c r="I38" s="166" t="s">
         <v>842</v>
       </c>
-      <c r="J38" s="166"/>
-      <c r="K38" s="167"/>
+      <c r="J38" s="167"/>
+      <c r="K38" s="168"/>
       <c r="L38" s="145"/>
       <c r="M38" s="145"/>
       <c r="N38" s="145"/>
@@ -20593,7 +20604,7 @@
       <c r="Y38" s="145"/>
     </row>
     <row r="39" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A39" s="145">
+      <c r="A39" s="172">
         <v>38</v>
       </c>
       <c r="B39" s="145" t="s">
@@ -20615,11 +20626,11 @@
         <v>0.5</v>
       </c>
       <c r="H39" s="145"/>
-      <c r="I39" s="165" t="s">
+      <c r="I39" s="166" t="s">
         <v>842</v>
       </c>
-      <c r="J39" s="166"/>
-      <c r="K39" s="167"/>
+      <c r="J39" s="167"/>
+      <c r="K39" s="168"/>
       <c r="L39" s="145"/>
       <c r="M39" s="145"/>
       <c r="N39" s="145"/>
@@ -20638,7 +20649,7 @@
       <c r="Y39" s="145"/>
     </row>
     <row r="40" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A40" s="145">
+      <c r="A40" s="172">
         <v>39</v>
       </c>
       <c r="B40" s="145" t="s">
@@ -20660,11 +20671,11 @@
         <v>0.5</v>
       </c>
       <c r="H40" s="139"/>
-      <c r="I40" s="165" t="s">
+      <c r="I40" s="166" t="s">
         <v>842</v>
       </c>
-      <c r="J40" s="166"/>
-      <c r="K40" s="167"/>
+      <c r="J40" s="167"/>
+      <c r="K40" s="168"/>
       <c r="L40" s="145"/>
       <c r="M40" s="145"/>
       <c r="N40" s="145"/>
@@ -20681,7 +20692,7 @@
       <c r="Y40" s="145"/>
     </row>
     <row r="41" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A41" s="145">
+      <c r="A41" s="172">
         <v>40</v>
       </c>
       <c r="B41" s="145" t="s">
@@ -20732,7 +20743,7 @@
       <c r="Y41" s="145"/>
     </row>
     <row r="42" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A42" s="145">
+      <c r="A42" s="172">
         <v>41</v>
       </c>
       <c r="B42" s="145" t="s">
@@ -20766,7 +20777,9 @@
       <c r="L42" s="33" t="s">
         <v>758</v>
       </c>
-      <c r="M42" s="145"/>
+      <c r="M42" s="145" t="s">
+        <v>691</v>
+      </c>
       <c r="N42" s="145"/>
       <c r="O42" s="145"/>
       <c r="P42" s="145"/>
@@ -20781,7 +20794,7 @@
       <c r="Y42" s="145"/>
     </row>
     <row r="43" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A43" s="145">
+      <c r="A43" s="172">
         <v>42</v>
       </c>
       <c r="B43" s="145" t="s">
@@ -20815,7 +20828,9 @@
       <c r="L43" s="33" t="s">
         <v>840</v>
       </c>
-      <c r="M43" s="145"/>
+      <c r="M43" s="145" t="s">
+        <v>691</v>
+      </c>
       <c r="N43" s="145"/>
       <c r="O43" s="145"/>
       <c r="P43" s="145"/>
@@ -20830,7 +20845,7 @@
       <c r="Y43" s="145"/>
     </row>
     <row r="44" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A44" s="145">
+      <c r="A44" s="172">
         <v>43</v>
       </c>
       <c r="B44" s="145" t="s">
@@ -20864,7 +20879,9 @@
       <c r="L44" s="33" t="s">
         <v>760</v>
       </c>
-      <c r="M44" s="145"/>
+      <c r="M44" s="145" t="s">
+        <v>691</v>
+      </c>
       <c r="N44" s="145"/>
       <c r="O44" s="145"/>
       <c r="P44" s="145"/>
@@ -20879,7 +20896,7 @@
       <c r="Y44" s="145"/>
     </row>
     <row r="45" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A45" s="145">
+      <c r="A45" s="172">
         <v>44</v>
       </c>
       <c r="B45" s="145" t="s">
@@ -20919,8 +20936,8 @@
       <c r="N45" s="145" t="s">
         <v>747</v>
       </c>
-      <c r="O45" s="145">
-        <v>1</v>
+      <c r="O45" s="145" t="s">
+        <v>693</v>
       </c>
       <c r="P45" s="145"/>
       <c r="Q45" s="145"/>
@@ -20934,7 +20951,7 @@
       <c r="Y45" s="145"/>
     </row>
     <row r="46" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A46" s="145">
+      <c r="A46" s="172">
         <v>45</v>
       </c>
       <c r="B46" s="145" t="s">
@@ -20974,8 +20991,8 @@
       <c r="N46" s="145" t="s">
         <v>748</v>
       </c>
-      <c r="O46" s="145">
-        <v>1</v>
+      <c r="O46" s="145" t="s">
+        <v>693</v>
       </c>
       <c r="P46" s="145"/>
       <c r="Q46" s="145"/>
@@ -20989,7 +21006,7 @@
       <c r="Y46" s="145"/>
     </row>
     <row r="47" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A47" s="145">
+      <c r="A47" s="172">
         <v>46</v>
       </c>
       <c r="B47" s="145" t="s">
@@ -21007,8 +21024,8 @@
       <c r="F47" s="145">
         <v>10</v>
       </c>
-      <c r="G47" s="146">
-        <v>1E-3</v>
+      <c r="G47" s="146" t="s">
+        <v>888</v>
       </c>
       <c r="H47" s="145"/>
       <c r="I47" s="145" t="s">
@@ -21029,8 +21046,8 @@
       <c r="N47" s="145" t="s">
         <v>749</v>
       </c>
-      <c r="O47" s="145">
-        <v>1</v>
+      <c r="O47" s="145" t="s">
+        <v>693</v>
       </c>
       <c r="P47" s="145"/>
       <c r="Q47" s="145"/>
@@ -21044,7 +21061,7 @@
       <c r="Y47" s="145"/>
     </row>
     <row r="48" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A48" s="145">
+      <c r="A48" s="172">
         <v>47</v>
       </c>
       <c r="B48" s="145" t="s">
@@ -21095,7 +21112,7 @@
       <c r="Y48" s="145"/>
     </row>
     <row r="49" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A49" s="145">
+      <c r="A49" s="172">
         <v>48</v>
       </c>
       <c r="B49" s="145" t="s">
@@ -21117,11 +21134,11 @@
         <v>0.1</v>
       </c>
       <c r="H49" s="145"/>
-      <c r="I49" s="162" t="s">
+      <c r="I49" s="163" t="s">
         <v>842</v>
       </c>
-      <c r="J49" s="163"/>
-      <c r="K49" s="164"/>
+      <c r="J49" s="164"/>
+      <c r="K49" s="165"/>
       <c r="L49" s="145"/>
       <c r="M49" s="145"/>
       <c r="N49" s="145"/>
@@ -21138,7 +21155,7 @@
       <c r="Y49" s="145"/>
     </row>
     <row r="50" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A50" s="145">
+      <c r="A50" s="172">
         <v>49</v>
       </c>
       <c r="B50" s="145" t="s">
@@ -21160,11 +21177,11 @@
         <v>0.1</v>
       </c>
       <c r="H50" s="145"/>
-      <c r="I50" s="161" t="s">
+      <c r="I50" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J50" s="161"/>
-      <c r="K50" s="161"/>
+      <c r="J50" s="153"/>
+      <c r="K50" s="153"/>
       <c r="L50" s="145"/>
       <c r="M50" s="145"/>
       <c r="N50" s="145"/>
@@ -21181,7 +21198,7 @@
       <c r="Y50" s="145"/>
     </row>
     <row r="51" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A51" s="145">
+      <c r="A51" s="172">
         <v>50</v>
       </c>
       <c r="B51" s="145" t="s">
@@ -21203,11 +21220,11 @@
         <v>0.1</v>
       </c>
       <c r="H51" s="145"/>
-      <c r="I51" s="161" t="s">
+      <c r="I51" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J51" s="161"/>
-      <c r="K51" s="161"/>
+      <c r="J51" s="153"/>
+      <c r="K51" s="153"/>
       <c r="L51" s="145"/>
       <c r="M51" s="145"/>
       <c r="N51" s="145"/>
@@ -21224,7 +21241,7 @@
       <c r="Y51" s="145"/>
     </row>
     <row r="52" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A52" s="145">
+      <c r="A52" s="172">
         <v>51</v>
       </c>
       <c r="B52" s="145" t="s">
@@ -21246,11 +21263,11 @@
         <v>0.1</v>
       </c>
       <c r="H52" s="145"/>
-      <c r="I52" s="161" t="s">
+      <c r="I52" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J52" s="161"/>
-      <c r="K52" s="161"/>
+      <c r="J52" s="153"/>
+      <c r="K52" s="153"/>
       <c r="L52" s="145"/>
       <c r="M52" s="145"/>
       <c r="N52" s="145"/>
@@ -21267,7 +21284,7 @@
       <c r="Y52" s="145"/>
     </row>
     <row r="53" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A53" s="145">
+      <c r="A53" s="172">
         <v>52</v>
       </c>
       <c r="B53" s="145" t="s">
@@ -21289,11 +21306,11 @@
         <v>0.1</v>
       </c>
       <c r="H53" s="145"/>
-      <c r="I53" s="161" t="s">
+      <c r="I53" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J53" s="161"/>
-      <c r="K53" s="161"/>
+      <c r="J53" s="153"/>
+      <c r="K53" s="153"/>
       <c r="L53" s="145"/>
       <c r="M53" s="145"/>
       <c r="N53" s="145"/>
@@ -21310,7 +21327,7 @@
       <c r="Y53" s="145"/>
     </row>
     <row r="54" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A54" s="145">
+      <c r="A54" s="172">
         <v>53</v>
       </c>
       <c r="B54" s="145" t="s">
@@ -21332,11 +21349,11 @@
         <v>0.1</v>
       </c>
       <c r="H54" s="145"/>
-      <c r="I54" s="161" t="s">
+      <c r="I54" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J54" s="161"/>
-      <c r="K54" s="161"/>
+      <c r="J54" s="153"/>
+      <c r="K54" s="153"/>
       <c r="L54" s="33"/>
       <c r="M54" s="33"/>
       <c r="N54" s="145"/>
@@ -21353,7 +21370,7 @@
       <c r="Y54" s="145"/>
     </row>
     <row r="55" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A55" s="145">
+      <c r="A55" s="172">
         <v>54</v>
       </c>
       <c r="B55" s="145" t="s">
@@ -21375,11 +21392,11 @@
         <v>0.1</v>
       </c>
       <c r="H55" s="145"/>
-      <c r="I55" s="161" t="s">
+      <c r="I55" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J55" s="161"/>
-      <c r="K55" s="161"/>
+      <c r="J55" s="153"/>
+      <c r="K55" s="153"/>
       <c r="L55" s="33"/>
       <c r="M55" s="33"/>
       <c r="N55" s="145"/>
@@ -21396,7 +21413,7 @@
       <c r="Y55" s="145"/>
     </row>
     <row r="56" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A56" s="145">
+      <c r="A56" s="172">
         <v>55</v>
       </c>
       <c r="B56" s="145" t="s">
@@ -21418,11 +21435,11 @@
         <v>0.1</v>
       </c>
       <c r="H56" s="145"/>
-      <c r="I56" s="161" t="s">
+      <c r="I56" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J56" s="161"/>
-      <c r="K56" s="161"/>
+      <c r="J56" s="153"/>
+      <c r="K56" s="153"/>
       <c r="L56" s="33"/>
       <c r="M56" s="33"/>
       <c r="N56" s="145"/>
@@ -21439,7 +21456,7 @@
       <c r="Y56" s="145"/>
     </row>
     <row r="57" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A57" s="145">
+      <c r="A57" s="172">
         <v>56</v>
       </c>
       <c r="B57" s="145" t="s">
@@ -21461,11 +21478,11 @@
         <v>0.1</v>
       </c>
       <c r="H57" s="145"/>
-      <c r="I57" s="161" t="s">
+      <c r="I57" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J57" s="161"/>
-      <c r="K57" s="161"/>
+      <c r="J57" s="153"/>
+      <c r="K57" s="153"/>
       <c r="L57" s="145"/>
       <c r="M57" s="145"/>
       <c r="N57" s="145"/>
@@ -21482,7 +21499,7 @@
       <c r="Y57" s="145"/>
     </row>
     <row r="58" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A58" s="145">
+      <c r="A58" s="172">
         <v>57</v>
       </c>
       <c r="B58" s="145" t="s">
@@ -21504,11 +21521,11 @@
         <v>0.1</v>
       </c>
       <c r="H58" s="145"/>
-      <c r="I58" s="161" t="s">
+      <c r="I58" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J58" s="161"/>
-      <c r="K58" s="161"/>
+      <c r="J58" s="153"/>
+      <c r="K58" s="153"/>
       <c r="L58" s="145"/>
       <c r="M58" s="145"/>
       <c r="N58" s="145"/>
@@ -21525,7 +21542,7 @@
       <c r="Y58" s="145"/>
     </row>
     <row r="59" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A59" s="145">
+      <c r="A59" s="172">
         <v>58</v>
       </c>
       <c r="B59" s="145" t="s">
@@ -21547,11 +21564,11 @@
         <v>0.1</v>
       </c>
       <c r="H59" s="145"/>
-      <c r="I59" s="161" t="s">
+      <c r="I59" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J59" s="161"/>
-      <c r="K59" s="161"/>
+      <c r="J59" s="153"/>
+      <c r="K59" s="153"/>
       <c r="L59" s="145"/>
       <c r="M59" s="33"/>
       <c r="N59" s="145"/>
@@ -21568,7 +21585,7 @@
       <c r="Y59" s="145"/>
     </row>
     <row r="60" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A60" s="145">
+      <c r="A60" s="172">
         <v>59</v>
       </c>
       <c r="B60" s="145" t="s">
@@ -21590,11 +21607,11 @@
         <v>0.1</v>
       </c>
       <c r="H60" s="145"/>
-      <c r="I60" s="161" t="s">
+      <c r="I60" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J60" s="161"/>
-      <c r="K60" s="161"/>
+      <c r="J60" s="153"/>
+      <c r="K60" s="153"/>
       <c r="L60" s="33"/>
       <c r="M60" s="33"/>
       <c r="N60" s="145"/>
@@ -21611,7 +21628,7 @@
       <c r="Y60" s="145"/>
     </row>
     <row r="61" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A61" s="145">
+      <c r="A61" s="172">
         <v>60</v>
       </c>
       <c r="B61" s="145" t="s">
@@ -21633,11 +21650,11 @@
         <v>0.1</v>
       </c>
       <c r="H61" s="145"/>
-      <c r="I61" s="161" t="s">
+      <c r="I61" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J61" s="161"/>
-      <c r="K61" s="161"/>
+      <c r="J61" s="153"/>
+      <c r="K61" s="153"/>
       <c r="L61" s="33"/>
       <c r="M61" s="33"/>
       <c r="N61" s="145"/>
@@ -21654,7 +21671,7 @@
       <c r="Y61" s="145"/>
     </row>
     <row r="62" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A62" s="145">
+      <c r="A62" s="172">
         <v>61</v>
       </c>
       <c r="B62" s="145" t="s">
@@ -21676,11 +21693,11 @@
         <v>0.1</v>
       </c>
       <c r="H62" s="145"/>
-      <c r="I62" s="161" t="s">
+      <c r="I62" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J62" s="161"/>
-      <c r="K62" s="161"/>
+      <c r="J62" s="153"/>
+      <c r="K62" s="153"/>
       <c r="L62" s="33"/>
       <c r="M62" s="33"/>
       <c r="N62" s="145"/>
@@ -21697,7 +21714,7 @@
       <c r="Y62" s="145"/>
     </row>
     <row r="63" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A63" s="145">
+      <c r="A63" s="172">
         <v>62</v>
       </c>
       <c r="B63" s="145" t="s">
@@ -21719,11 +21736,11 @@
         <v>0.1</v>
       </c>
       <c r="H63" s="145"/>
-      <c r="I63" s="161" t="s">
+      <c r="I63" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J63" s="161"/>
-      <c r="K63" s="161"/>
+      <c r="J63" s="153"/>
+      <c r="K63" s="153"/>
       <c r="L63" s="33"/>
       <c r="M63" s="33"/>
       <c r="N63" s="33"/>
@@ -21740,7 +21757,7 @@
       <c r="Y63" s="145"/>
     </row>
     <row r="64" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A64" s="145">
+      <c r="A64" s="172">
         <v>63</v>
       </c>
       <c r="B64" s="145" t="s">
@@ -21762,11 +21779,11 @@
         <v>1</v>
       </c>
       <c r="H64" s="145"/>
-      <c r="I64" s="161" t="s">
+      <c r="I64" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J64" s="161"/>
-      <c r="K64" s="161"/>
+      <c r="J64" s="153"/>
+      <c r="K64" s="153"/>
       <c r="L64" s="33"/>
       <c r="M64" s="33"/>
       <c r="N64" s="33"/>
@@ -21783,7 +21800,7 @@
       <c r="Y64" s="145"/>
     </row>
     <row r="65" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A65" s="145">
+      <c r="A65" s="172">
         <v>64</v>
       </c>
       <c r="B65" s="145" t="s">
@@ -21842,7 +21859,7 @@
       <c r="Y65" s="145"/>
     </row>
     <row r="66" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A66" s="145">
+      <c r="A66" s="172">
         <v>65</v>
       </c>
       <c r="B66" s="145" t="s">
@@ -21864,11 +21881,11 @@
         <v>0.2</v>
       </c>
       <c r="H66" s="145"/>
-      <c r="I66" s="161" t="s">
+      <c r="I66" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J66" s="161"/>
-      <c r="K66" s="161"/>
+      <c r="J66" s="153"/>
+      <c r="K66" s="153"/>
       <c r="L66" s="145"/>
       <c r="M66" s="145"/>
       <c r="N66" s="145"/>
@@ -21885,7 +21902,7 @@
       <c r="Y66" s="145"/>
     </row>
     <row r="67" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A67" s="145">
+      <c r="A67" s="172">
         <v>66</v>
       </c>
       <c r="B67" s="145" t="s">
@@ -21942,7 +21959,7 @@
       <c r="Y67" s="145"/>
     </row>
     <row r="68" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A68" s="145">
+      <c r="A68" s="172">
         <v>67</v>
       </c>
       <c r="B68" s="145" t="s">
@@ -21999,7 +22016,7 @@
       <c r="Y68" s="145"/>
     </row>
     <row r="69" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A69" s="145">
+      <c r="A69" s="172">
         <v>68</v>
       </c>
       <c r="B69" s="145" t="s">
@@ -22058,7 +22075,7 @@
       <c r="Y69" s="145"/>
     </row>
     <row r="70" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A70" s="145">
+      <c r="A70" s="172">
         <v>69</v>
       </c>
       <c r="B70" s="145" t="s">
@@ -22115,7 +22132,7 @@
       <c r="Y70" s="145"/>
     </row>
     <row r="71" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A71" s="145">
+      <c r="A71" s="172">
         <v>70</v>
       </c>
       <c r="B71" s="145" t="s">
@@ -22172,7 +22189,7 @@
       <c r="Y71" s="145"/>
     </row>
     <row r="72" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A72" s="145">
+      <c r="A72" s="172">
         <v>71</v>
       </c>
       <c r="B72" s="145" t="s">
@@ -22231,7 +22248,7 @@
       <c r="Y72" s="145"/>
     </row>
     <row r="73" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A73" s="145">
+      <c r="A73" s="172">
         <v>72</v>
       </c>
       <c r="B73" s="145" t="s">
@@ -22288,7 +22305,7 @@
       <c r="Y73" s="145"/>
     </row>
     <row r="74" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A74" s="145">
+      <c r="A74" s="172">
         <v>73</v>
       </c>
       <c r="B74" s="145" t="s">
@@ -22345,7 +22362,7 @@
       <c r="Y74" s="145"/>
     </row>
     <row r="75" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A75" s="145">
+      <c r="A75" s="172">
         <v>74</v>
       </c>
       <c r="B75" s="145" t="s">
@@ -22404,7 +22421,7 @@
       <c r="Y75" s="145"/>
     </row>
     <row r="76" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A76" s="145">
+      <c r="A76" s="172">
         <v>75</v>
       </c>
       <c r="B76" s="145" t="s">
@@ -22463,7 +22480,7 @@
       <c r="Y76" s="145"/>
     </row>
     <row r="77" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A77" s="145">
+      <c r="A77" s="172">
         <v>76</v>
       </c>
       <c r="B77" s="145" t="s">
@@ -22522,7 +22539,7 @@
       <c r="Y77" s="145"/>
     </row>
     <row r="78" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A78" s="145">
+      <c r="A78" s="172">
         <v>77</v>
       </c>
       <c r="B78" s="145" t="s">
@@ -22544,11 +22561,11 @@
         <v>0.5</v>
       </c>
       <c r="H78" s="145"/>
-      <c r="I78" s="161" t="s">
+      <c r="I78" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J78" s="161"/>
-      <c r="K78" s="161"/>
+      <c r="J78" s="153"/>
+      <c r="K78" s="153"/>
       <c r="L78" s="145"/>
       <c r="M78" s="145"/>
       <c r="N78" s="145"/>
@@ -22565,7 +22582,7 @@
       <c r="Y78" s="145"/>
     </row>
     <row r="79" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A79" s="145">
+      <c r="A79" s="172">
         <v>78</v>
       </c>
       <c r="B79" s="145" t="s">
@@ -22587,11 +22604,11 @@
         <v>0.5</v>
       </c>
       <c r="H79" s="145"/>
-      <c r="I79" s="161" t="s">
+      <c r="I79" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J79" s="161"/>
-      <c r="K79" s="161"/>
+      <c r="J79" s="153"/>
+      <c r="K79" s="153"/>
       <c r="L79" s="145"/>
       <c r="M79" s="145"/>
       <c r="N79" s="145"/>
@@ -22608,7 +22625,7 @@
       <c r="Y79" s="145"/>
     </row>
     <row r="80" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A80" s="145">
+      <c r="A80" s="172">
         <v>79</v>
       </c>
       <c r="B80" s="145" t="s">
@@ -22632,11 +22649,11 @@
       <c r="H80" s="145" t="s">
         <v>791</v>
       </c>
-      <c r="I80" s="161" t="s">
+      <c r="I80" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J80" s="161"/>
-      <c r="K80" s="161"/>
+      <c r="J80" s="153"/>
+      <c r="K80" s="153"/>
       <c r="L80" s="145"/>
       <c r="M80" s="145"/>
       <c r="N80" s="145"/>
@@ -22653,7 +22670,7 @@
       <c r="Y80" s="145"/>
     </row>
     <row r="81" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A81" s="145">
+      <c r="A81" s="172">
         <v>80</v>
       </c>
       <c r="B81" s="145" t="s">
@@ -22677,11 +22694,11 @@
       <c r="H81" s="145" t="s">
         <v>791</v>
       </c>
-      <c r="I81" s="161" t="s">
+      <c r="I81" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J81" s="161"/>
-      <c r="K81" s="161"/>
+      <c r="J81" s="153"/>
+      <c r="K81" s="153"/>
       <c r="L81" s="145"/>
       <c r="M81" s="145"/>
       <c r="N81" s="145"/>
@@ -22698,7 +22715,7 @@
       <c r="Y81" s="145"/>
     </row>
     <row r="82" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A82" s="145">
+      <c r="A82" s="172">
         <v>81</v>
       </c>
       <c r="B82" s="145" t="s">
@@ -22722,11 +22739,11 @@
       <c r="H82" s="145" t="s">
         <v>794</v>
       </c>
-      <c r="I82" s="161" t="s">
+      <c r="I82" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J82" s="161"/>
-      <c r="K82" s="161"/>
+      <c r="J82" s="153"/>
+      <c r="K82" s="153"/>
       <c r="L82" s="145"/>
       <c r="M82" s="145"/>
       <c r="N82" s="145"/>
@@ -22743,7 +22760,7 @@
       <c r="Y82" s="145"/>
     </row>
     <row r="83" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A83" s="145">
+      <c r="A83" s="172">
         <v>82</v>
       </c>
       <c r="B83" s="145" t="s">
@@ -22767,11 +22784,11 @@
       <c r="H83" s="145" t="s">
         <v>794</v>
       </c>
-      <c r="I83" s="161" t="s">
+      <c r="I83" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J83" s="161"/>
-      <c r="K83" s="161"/>
+      <c r="J83" s="153"/>
+      <c r="K83" s="153"/>
       <c r="L83" s="145"/>
       <c r="M83" s="145"/>
       <c r="N83" s="145"/>
@@ -22788,7 +22805,7 @@
       <c r="Y83" s="145"/>
     </row>
     <row r="84" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A84" s="145">
+      <c r="A84" s="172">
         <v>83</v>
       </c>
       <c r="B84" s="145" t="s">
@@ -22812,11 +22829,11 @@
       <c r="H84" s="145" t="s">
         <v>797</v>
       </c>
-      <c r="I84" s="161" t="s">
+      <c r="I84" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J84" s="161"/>
-      <c r="K84" s="161"/>
+      <c r="J84" s="153"/>
+      <c r="K84" s="153"/>
       <c r="L84" s="145"/>
       <c r="M84" s="145"/>
       <c r="N84" s="145"/>
@@ -22833,7 +22850,7 @@
       <c r="Y84" s="145"/>
     </row>
     <row r="85" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A85" s="145">
+      <c r="A85" s="172">
         <v>84</v>
       </c>
       <c r="B85" s="145" t="s">
@@ -22857,11 +22874,11 @@
       <c r="H85" s="145" t="s">
         <v>797</v>
       </c>
-      <c r="I85" s="161" t="s">
+      <c r="I85" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J85" s="161"/>
-      <c r="K85" s="161"/>
+      <c r="J85" s="153"/>
+      <c r="K85" s="153"/>
       <c r="L85" s="145"/>
       <c r="M85" s="145"/>
       <c r="N85" s="145"/>
@@ -22878,7 +22895,7 @@
       <c r="Y85" s="145"/>
     </row>
     <row r="86" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A86" s="145">
+      <c r="A86" s="172">
         <v>85</v>
       </c>
       <c r="B86" s="145" t="s">
@@ -22902,11 +22919,11 @@
       <c r="H86" s="145" t="s">
         <v>800</v>
       </c>
-      <c r="I86" s="161" t="s">
+      <c r="I86" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J86" s="161"/>
-      <c r="K86" s="161"/>
+      <c r="J86" s="153"/>
+      <c r="K86" s="153"/>
       <c r="L86" s="145"/>
       <c r="M86" s="145"/>
       <c r="N86" s="145"/>
@@ -22923,7 +22940,7 @@
       <c r="Y86" s="145"/>
     </row>
     <row r="87" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A87" s="145">
+      <c r="A87" s="172">
         <v>86</v>
       </c>
       <c r="B87" s="145" t="s">
@@ -22976,7 +22993,7 @@
       <c r="Y87" s="145"/>
     </row>
     <row r="88" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A88" s="145">
+      <c r="A88" s="172">
         <v>87</v>
       </c>
       <c r="B88" s="145" t="s">
@@ -23033,7 +23050,7 @@
       <c r="Y88" s="145"/>
     </row>
     <row r="89" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A89" s="145">
+      <c r="A89" s="172">
         <v>88</v>
       </c>
       <c r="B89" s="145" t="s">
@@ -23057,11 +23074,11 @@
       <c r="H89" s="145" t="s">
         <v>800</v>
       </c>
-      <c r="I89" s="161" t="s">
+      <c r="I89" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J89" s="161"/>
-      <c r="K89" s="161"/>
+      <c r="J89" s="153"/>
+      <c r="K89" s="153"/>
       <c r="L89" s="145"/>
       <c r="M89" s="145"/>
       <c r="N89" s="145"/>
@@ -23078,7 +23095,7 @@
       <c r="Y89" s="145"/>
     </row>
     <row r="90" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A90" s="145">
+      <c r="A90" s="172">
         <v>89</v>
       </c>
       <c r="B90" s="145" t="s">
@@ -23131,7 +23148,7 @@
       <c r="Y90" s="145"/>
     </row>
     <row r="91" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A91" s="145">
+      <c r="A91" s="172">
         <v>90</v>
       </c>
       <c r="B91" s="145" t="s">
@@ -23188,7 +23205,7 @@
       <c r="Y91" s="145"/>
     </row>
     <row r="92" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A92" s="145">
+      <c r="A92" s="172">
         <v>91</v>
       </c>
       <c r="B92" s="145" t="s">
@@ -23243,7 +23260,7 @@
       <c r="Y92" s="145"/>
     </row>
     <row r="93" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A93" s="145">
+      <c r="A93" s="172">
         <v>92</v>
       </c>
       <c r="B93" s="145" t="s">
@@ -23298,7 +23315,7 @@
       <c r="Y93" s="145"/>
     </row>
     <row r="94" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A94" s="145">
+      <c r="A94" s="172">
         <v>93</v>
       </c>
       <c r="B94" s="145" t="s">
@@ -23312,11 +23329,11 @@
         <v>0.1</v>
       </c>
       <c r="H94" s="145"/>
-      <c r="I94" s="161" t="s">
+      <c r="I94" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J94" s="161"/>
-      <c r="K94" s="161"/>
+      <c r="J94" s="153"/>
+      <c r="K94" s="153"/>
       <c r="L94" s="145"/>
       <c r="M94" s="145"/>
       <c r="N94" s="145"/>
@@ -23333,7 +23350,7 @@
       <c r="Y94" s="145"/>
     </row>
     <row r="95" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A95" s="145">
+      <c r="A95" s="172">
         <v>94</v>
       </c>
       <c r="B95" s="145" t="s">
@@ -23347,11 +23364,11 @@
         <v>0.1</v>
       </c>
       <c r="H95" s="145"/>
-      <c r="I95" s="161" t="s">
+      <c r="I95" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J95" s="161"/>
-      <c r="K95" s="161"/>
+      <c r="J95" s="153"/>
+      <c r="K95" s="153"/>
       <c r="L95" s="145"/>
       <c r="M95" s="145"/>
       <c r="N95" s="145"/>
@@ -23368,7 +23385,7 @@
       <c r="Y95" s="145"/>
     </row>
     <row r="96" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A96" s="145">
+      <c r="A96" s="172">
         <v>95</v>
       </c>
       <c r="B96" s="145" t="s">
@@ -23382,11 +23399,11 @@
         <v>0.1</v>
       </c>
       <c r="H96" s="145"/>
-      <c r="I96" s="161" t="s">
+      <c r="I96" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J96" s="161"/>
-      <c r="K96" s="161"/>
+      <c r="J96" s="153"/>
+      <c r="K96" s="153"/>
       <c r="L96" s="145"/>
       <c r="M96" s="145"/>
       <c r="N96" s="145"/>
@@ -23403,7 +23420,7 @@
       <c r="Y96" s="145"/>
     </row>
     <row r="97" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A97" s="145">
+      <c r="A97" s="172">
         <v>96</v>
       </c>
       <c r="B97" s="145" t="s">
@@ -23417,11 +23434,11 @@
         <v>0.1</v>
       </c>
       <c r="H97" s="145"/>
-      <c r="I97" s="161" t="s">
+      <c r="I97" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J97" s="161"/>
-      <c r="K97" s="161"/>
+      <c r="J97" s="153"/>
+      <c r="K97" s="153"/>
       <c r="L97" s="145"/>
       <c r="M97" s="145"/>
       <c r="N97" s="145"/>
@@ -23438,7 +23455,7 @@
       <c r="Y97" s="145"/>
     </row>
     <row r="98" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A98" s="145">
+      <c r="A98" s="172">
         <v>97</v>
       </c>
       <c r="B98" s="145" t="s">
@@ -23452,11 +23469,11 @@
         <v>0.1</v>
       </c>
       <c r="H98" s="145"/>
-      <c r="I98" s="161" t="s">
+      <c r="I98" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J98" s="161"/>
-      <c r="K98" s="161"/>
+      <c r="J98" s="153"/>
+      <c r="K98" s="153"/>
       <c r="L98" s="145"/>
       <c r="M98" s="145"/>
       <c r="N98" s="145"/>
@@ -23473,7 +23490,7 @@
       <c r="Y98" s="145"/>
     </row>
     <row r="99" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A99" s="145">
+      <c r="A99" s="172">
         <v>98</v>
       </c>
       <c r="B99" s="145" t="s">
@@ -23487,11 +23504,11 @@
         <v>0.1</v>
       </c>
       <c r="H99" s="145"/>
-      <c r="I99" s="161" t="s">
+      <c r="I99" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J99" s="161"/>
-      <c r="K99" s="161"/>
+      <c r="J99" s="153"/>
+      <c r="K99" s="153"/>
       <c r="L99" s="145"/>
       <c r="M99" s="145"/>
       <c r="N99" s="145"/>
@@ -23508,7 +23525,7 @@
       <c r="Y99" s="145"/>
     </row>
     <row r="100" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A100" s="145">
+      <c r="A100" s="172">
         <v>99</v>
       </c>
       <c r="B100" s="145" t="s">
@@ -23522,11 +23539,11 @@
         <v>0.1</v>
       </c>
       <c r="H100" s="145"/>
-      <c r="I100" s="161" t="s">
+      <c r="I100" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J100" s="161"/>
-      <c r="K100" s="161"/>
+      <c r="J100" s="153"/>
+      <c r="K100" s="153"/>
       <c r="L100" s="145"/>
       <c r="M100" s="145"/>
       <c r="N100" s="145"/>
@@ -23543,7 +23560,7 @@
       <c r="Y100" s="145"/>
     </row>
     <row r="101" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A101" s="145">
+      <c r="A101" s="172">
         <v>100</v>
       </c>
       <c r="B101" s="145" t="s">
@@ -23557,11 +23574,11 @@
         <v>0.1</v>
       </c>
       <c r="H101" s="145"/>
-      <c r="I101" s="161" t="s">
+      <c r="I101" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J101" s="161"/>
-      <c r="K101" s="161"/>
+      <c r="J101" s="153"/>
+      <c r="K101" s="153"/>
       <c r="L101" s="145"/>
       <c r="M101" s="145"/>
       <c r="N101" s="145"/>
@@ -23578,7 +23595,7 @@
       <c r="Y101" s="145"/>
     </row>
     <row r="102" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A102" s="145">
+      <c r="A102" s="172">
         <v>101</v>
       </c>
       <c r="B102" s="145" t="s">
@@ -23592,11 +23609,11 @@
         <v>0.1</v>
       </c>
       <c r="H102" s="145"/>
-      <c r="I102" s="161" t="s">
+      <c r="I102" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J102" s="161"/>
-      <c r="K102" s="161"/>
+      <c r="J102" s="153"/>
+      <c r="K102" s="153"/>
       <c r="L102" s="145"/>
       <c r="M102" s="145"/>
       <c r="N102" s="145"/>
@@ -23613,7 +23630,7 @@
       <c r="Y102" s="145"/>
     </row>
     <row r="103" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A103" s="145">
+      <c r="A103" s="172">
         <v>102</v>
       </c>
       <c r="B103" s="145" t="s">
@@ -23627,11 +23644,11 @@
         <v>0.1</v>
       </c>
       <c r="H103" s="145"/>
-      <c r="I103" s="161" t="s">
+      <c r="I103" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J103" s="161"/>
-      <c r="K103" s="161"/>
+      <c r="J103" s="153"/>
+      <c r="K103" s="153"/>
       <c r="L103" s="145"/>
       <c r="M103" s="145"/>
       <c r="N103" s="145"/>
@@ -23648,7 +23665,7 @@
       <c r="Y103" s="145"/>
     </row>
     <row r="104" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A104" s="145">
+      <c r="A104" s="172">
         <v>103</v>
       </c>
       <c r="B104" s="145" t="s">
@@ -23662,11 +23679,11 @@
         <v>0.1</v>
       </c>
       <c r="H104" s="145"/>
-      <c r="I104" s="161" t="s">
+      <c r="I104" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J104" s="161"/>
-      <c r="K104" s="161"/>
+      <c r="J104" s="153"/>
+      <c r="K104" s="153"/>
       <c r="L104" s="145"/>
       <c r="M104" s="145"/>
       <c r="N104" s="145"/>
@@ -23683,7 +23700,7 @@
       <c r="Y104" s="145"/>
     </row>
     <row r="105" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A105" s="145">
+      <c r="A105" s="172">
         <v>104</v>
       </c>
       <c r="B105" s="145" t="s">
@@ -23697,11 +23714,11 @@
         <v>0.1</v>
       </c>
       <c r="H105" s="145"/>
-      <c r="I105" s="161" t="s">
+      <c r="I105" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J105" s="161"/>
-      <c r="K105" s="161"/>
+      <c r="J105" s="153"/>
+      <c r="K105" s="153"/>
       <c r="L105" s="145"/>
       <c r="M105" s="145"/>
       <c r="N105" s="145"/>
@@ -23718,7 +23735,7 @@
       <c r="Y105" s="145"/>
     </row>
     <row r="106" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A106" s="145">
+      <c r="A106" s="172">
         <v>105</v>
       </c>
       <c r="B106" s="145" t="s">
@@ -23732,11 +23749,11 @@
         <v>0.1</v>
       </c>
       <c r="H106" s="145"/>
-      <c r="I106" s="161" t="s">
+      <c r="I106" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J106" s="161"/>
-      <c r="K106" s="161"/>
+      <c r="J106" s="153"/>
+      <c r="K106" s="153"/>
       <c r="L106" s="145"/>
       <c r="M106" s="145"/>
       <c r="N106" s="145"/>
@@ -23753,7 +23770,7 @@
       <c r="Y106" s="145"/>
     </row>
     <row r="107" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A107" s="145">
+      <c r="A107" s="172">
         <v>106</v>
       </c>
       <c r="B107" s="145" t="s">
@@ -23767,11 +23784,11 @@
         <v>0.1</v>
       </c>
       <c r="H107" s="145"/>
-      <c r="I107" s="161" t="s">
+      <c r="I107" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J107" s="161"/>
-      <c r="K107" s="161"/>
+      <c r="J107" s="153"/>
+      <c r="K107" s="153"/>
       <c r="L107" s="145"/>
       <c r="M107" s="145"/>
       <c r="N107" s="145"/>
@@ -23788,7 +23805,7 @@
       <c r="Y107" s="145"/>
     </row>
     <row r="108" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A108" s="145">
+      <c r="A108" s="172">
         <v>107</v>
       </c>
       <c r="B108" s="145" t="s">
@@ -23802,11 +23819,11 @@
         <v>0.1</v>
       </c>
       <c r="H108" s="145"/>
-      <c r="I108" s="161" t="s">
+      <c r="I108" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J108" s="161"/>
-      <c r="K108" s="161"/>
+      <c r="J108" s="153"/>
+      <c r="K108" s="153"/>
       <c r="L108" s="145"/>
       <c r="M108" s="145"/>
       <c r="N108" s="145"/>
@@ -23823,7 +23840,7 @@
       <c r="Y108" s="145"/>
     </row>
     <row r="109" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A109" s="145">
+      <c r="A109" s="172">
         <v>108</v>
       </c>
       <c r="B109" s="145" t="s">
@@ -23837,11 +23854,11 @@
         <v>0.1</v>
       </c>
       <c r="H109" s="145"/>
-      <c r="I109" s="161" t="s">
+      <c r="I109" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J109" s="161"/>
-      <c r="K109" s="161"/>
+      <c r="J109" s="153"/>
+      <c r="K109" s="153"/>
       <c r="L109" s="145"/>
       <c r="M109" s="145"/>
       <c r="N109" s="145"/>
@@ -23858,7 +23875,7 @@
       <c r="Y109" s="145"/>
     </row>
     <row r="110" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A110" s="145">
+      <c r="A110" s="172">
         <v>109</v>
       </c>
       <c r="B110" s="145" t="s">
@@ -23872,11 +23889,11 @@
         <v>0.1</v>
       </c>
       <c r="H110" s="145"/>
-      <c r="I110" s="161" t="s">
+      <c r="I110" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J110" s="161"/>
-      <c r="K110" s="161"/>
+      <c r="J110" s="153"/>
+      <c r="K110" s="153"/>
       <c r="L110" s="145"/>
       <c r="M110" s="145"/>
       <c r="N110" s="145"/>
@@ -23893,7 +23910,7 @@
       <c r="Y110" s="145"/>
     </row>
     <row r="111" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A111" s="145">
+      <c r="A111" s="172">
         <v>110</v>
       </c>
       <c r="B111" s="145" t="s">
@@ -23907,11 +23924,11 @@
         <v>0.1</v>
       </c>
       <c r="H111" s="145"/>
-      <c r="I111" s="161" t="s">
+      <c r="I111" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J111" s="161"/>
-      <c r="K111" s="161"/>
+      <c r="J111" s="153"/>
+      <c r="K111" s="153"/>
       <c r="L111" s="145"/>
       <c r="M111" s="145"/>
       <c r="N111" s="145"/>
@@ -23928,7 +23945,7 @@
       <c r="Y111" s="145"/>
     </row>
     <row r="112" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A112" s="145">
+      <c r="A112" s="172">
         <v>111</v>
       </c>
       <c r="B112" s="145" t="s">
@@ -23942,11 +23959,11 @@
         <v>0.1</v>
       </c>
       <c r="H112" s="145"/>
-      <c r="I112" s="161" t="s">
+      <c r="I112" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J112" s="161"/>
-      <c r="K112" s="161"/>
+      <c r="J112" s="153"/>
+      <c r="K112" s="153"/>
       <c r="L112" s="145"/>
       <c r="M112" s="145"/>
       <c r="N112" s="145"/>
@@ -23963,7 +23980,7 @@
       <c r="Y112" s="145"/>
     </row>
     <row r="113" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A113" s="145">
+      <c r="A113" s="172">
         <v>112</v>
       </c>
       <c r="B113" s="145" t="s">
@@ -23977,11 +23994,11 @@
         <v>0.1</v>
       </c>
       <c r="H113" s="145"/>
-      <c r="I113" s="161" t="s">
+      <c r="I113" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J113" s="161"/>
-      <c r="K113" s="161"/>
+      <c r="J113" s="153"/>
+      <c r="K113" s="153"/>
       <c r="L113" s="145"/>
       <c r="M113" s="145"/>
       <c r="N113" s="145"/>
@@ -23998,7 +24015,7 @@
       <c r="Y113" s="145"/>
     </row>
     <row r="114" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A114" s="145" t="s">
+      <c r="A114" s="172" t="s">
         <v>885</v>
       </c>
       <c r="B114" s="145" t="s">
@@ -24012,11 +24029,11 @@
         <v>0.1</v>
       </c>
       <c r="H114" s="145"/>
-      <c r="I114" s="161" t="s">
+      <c r="I114" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J114" s="161"/>
-      <c r="K114" s="161"/>
+      <c r="J114" s="153"/>
+      <c r="K114" s="153"/>
       <c r="L114" s="145"/>
       <c r="M114" s="145"/>
       <c r="N114" s="145"/>
@@ -24033,7 +24050,7 @@
       <c r="Y114" s="145"/>
     </row>
     <row r="115" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A115" s="145" t="s">
+      <c r="A115" s="172" t="s">
         <v>857</v>
       </c>
       <c r="B115" s="145" t="s">
@@ -24049,11 +24066,11 @@
         <v>883</v>
       </c>
       <c r="H115" s="145"/>
-      <c r="I115" s="161" t="s">
+      <c r="I115" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J115" s="161"/>
-      <c r="K115" s="161"/>
+      <c r="J115" s="153"/>
+      <c r="K115" s="153"/>
       <c r="L115" s="145"/>
       <c r="M115" s="145"/>
       <c r="N115" s="145"/>
@@ -24070,7 +24087,7 @@
       <c r="Y115" s="145"/>
     </row>
     <row r="116" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A116" s="145" t="s">
+      <c r="A116" s="172" t="s">
         <v>860</v>
       </c>
       <c r="B116" s="145" t="s">
@@ -24086,11 +24103,11 @@
         <v>883</v>
       </c>
       <c r="H116" s="145"/>
-      <c r="I116" s="161" t="s">
+      <c r="I116" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J116" s="161"/>
-      <c r="K116" s="161"/>
+      <c r="J116" s="153"/>
+      <c r="K116" s="153"/>
       <c r="L116" s="145"/>
       <c r="M116" s="145"/>
       <c r="N116" s="145"/>
@@ -24107,7 +24124,7 @@
       <c r="Y116" s="145"/>
     </row>
     <row r="117" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A117" s="145" t="s">
+      <c r="A117" s="172" t="s">
         <v>877</v>
       </c>
       <c r="B117" s="145" t="s">
@@ -24123,11 +24140,11 @@
         <v>884</v>
       </c>
       <c r="H117" s="145"/>
-      <c r="I117" s="161" t="s">
+      <c r="I117" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J117" s="161"/>
-      <c r="K117" s="161"/>
+      <c r="J117" s="153"/>
+      <c r="K117" s="153"/>
       <c r="L117" s="145"/>
       <c r="M117" s="145"/>
       <c r="N117" s="145"/>
@@ -24144,7 +24161,7 @@
       <c r="Y117" s="145"/>
     </row>
     <row r="118" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A118" s="145" t="s">
+      <c r="A118" s="172" t="s">
         <v>878</v>
       </c>
       <c r="B118" s="145" t="s">
@@ -24160,11 +24177,11 @@
         <v>884</v>
       </c>
       <c r="H118" s="145"/>
-      <c r="I118" s="161" t="s">
+      <c r="I118" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J118" s="161"/>
-      <c r="K118" s="161"/>
+      <c r="J118" s="153"/>
+      <c r="K118" s="153"/>
       <c r="L118" s="145"/>
       <c r="M118" s="145"/>
       <c r="N118" s="145"/>
@@ -24181,7 +24198,7 @@
       <c r="Y118" s="145"/>
     </row>
     <row r="119" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A119" s="145" t="s">
+      <c r="A119" s="172" t="s">
         <v>879</v>
       </c>
       <c r="B119" s="145" t="s">
@@ -24197,11 +24214,11 @@
         <v>884</v>
       </c>
       <c r="H119" s="145"/>
-      <c r="I119" s="161" t="s">
+      <c r="I119" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J119" s="161"/>
-      <c r="K119" s="161"/>
+      <c r="J119" s="153"/>
+      <c r="K119" s="153"/>
       <c r="L119" s="145"/>
       <c r="M119" s="145"/>
       <c r="N119" s="145"/>
@@ -24218,7 +24235,7 @@
       <c r="Y119" s="145"/>
     </row>
     <row r="120" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A120" s="145" t="s">
+      <c r="A120" s="172" t="s">
         <v>880</v>
       </c>
       <c r="B120" s="145" t="s">
@@ -24234,11 +24251,11 @@
         <v>884</v>
       </c>
       <c r="H120" s="145"/>
-      <c r="I120" s="161" t="s">
+      <c r="I120" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J120" s="161"/>
-      <c r="K120" s="161"/>
+      <c r="J120" s="153"/>
+      <c r="K120" s="153"/>
       <c r="L120" s="145"/>
       <c r="M120" s="145"/>
       <c r="N120" s="145"/>
@@ -24255,7 +24272,7 @@
       <c r="Y120" s="145"/>
     </row>
     <row r="121" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A121" s="145" t="s">
+      <c r="A121" s="172" t="s">
         <v>881</v>
       </c>
       <c r="B121" s="145" t="s">
@@ -24271,11 +24288,11 @@
         <v>884</v>
       </c>
       <c r="H121" s="145"/>
-      <c r="I121" s="161" t="s">
+      <c r="I121" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J121" s="161"/>
-      <c r="K121" s="161"/>
+      <c r="J121" s="153"/>
+      <c r="K121" s="153"/>
       <c r="L121" s="145"/>
       <c r="M121" s="145"/>
       <c r="N121" s="145"/>
@@ -24292,10 +24309,10 @@
       <c r="Y121" s="145"/>
     </row>
     <row r="122" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A122" s="145" t="s">
+      <c r="A122" s="172" t="s">
         <v>882</v>
       </c>
-      <c r="B122" s="171" t="s">
+      <c r="B122" s="152" t="s">
         <v>865</v>
       </c>
       <c r="C122" s="145" t="s">
@@ -24308,11 +24325,11 @@
         <v>884</v>
       </c>
       <c r="H122" s="145"/>
-      <c r="I122" s="161" t="s">
+      <c r="I122" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="J122" s="161"/>
-      <c r="K122" s="161"/>
+      <c r="J122" s="153"/>
+      <c r="K122" s="153"/>
       <c r="L122" s="145"/>
       <c r="M122" s="145"/>
       <c r="N122" s="145"/>
@@ -24330,7 +24347,7 @@
     </row>
     <row r="123" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A123" s="145"/>
-      <c r="B123" s="171"/>
+      <c r="B123" s="152"/>
     </row>
     <row r="124" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="125" spans="1:25" ht="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -24360,40 +24377,27 @@
     <row r="149" s="133" customFormat="1" ht="29.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
   <mergeCells count="68">
-    <mergeCell ref="I110:K110"/>
-    <mergeCell ref="I111:K111"/>
-    <mergeCell ref="I112:K112"/>
-    <mergeCell ref="I113:K113"/>
-    <mergeCell ref="I114:K114"/>
-    <mergeCell ref="I97:K97"/>
-    <mergeCell ref="I80:K80"/>
-    <mergeCell ref="I81:K81"/>
-    <mergeCell ref="I82:K82"/>
-    <mergeCell ref="I83:K83"/>
-    <mergeCell ref="I84:K84"/>
-    <mergeCell ref="I86:K86"/>
-    <mergeCell ref="I89:K89"/>
-    <mergeCell ref="I94:K94"/>
-    <mergeCell ref="I95:K95"/>
-    <mergeCell ref="I96:K96"/>
-    <mergeCell ref="I108:K108"/>
-    <mergeCell ref="I109:K109"/>
-    <mergeCell ref="I98:K98"/>
-    <mergeCell ref="I99:K99"/>
-    <mergeCell ref="I100:K100"/>
-    <mergeCell ref="I101:K101"/>
-    <mergeCell ref="I102:K102"/>
-    <mergeCell ref="I103:K103"/>
-    <mergeCell ref="I104:K104"/>
-    <mergeCell ref="I105:K105"/>
-    <mergeCell ref="I106:K106"/>
-    <mergeCell ref="I107:K107"/>
-    <mergeCell ref="I85:K85"/>
-    <mergeCell ref="I62:K62"/>
-    <mergeCell ref="I63:K63"/>
-    <mergeCell ref="I64:K64"/>
-    <mergeCell ref="I66:K66"/>
-    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="I120:K120"/>
+    <mergeCell ref="I121:K121"/>
+    <mergeCell ref="I122:K122"/>
+    <mergeCell ref="I115:K115"/>
+    <mergeCell ref="I116:K116"/>
+    <mergeCell ref="I117:K117"/>
+    <mergeCell ref="I118:K118"/>
+    <mergeCell ref="I119:K119"/>
+    <mergeCell ref="I49:K49"/>
+    <mergeCell ref="I6:K6"/>
+    <mergeCell ref="I7:K7"/>
+    <mergeCell ref="I8:K8"/>
+    <mergeCell ref="I9:K9"/>
+    <mergeCell ref="I16:K16"/>
+    <mergeCell ref="I17:K17"/>
+    <mergeCell ref="I18:K18"/>
+    <mergeCell ref="I21:K21"/>
+    <mergeCell ref="I38:K38"/>
+    <mergeCell ref="I39:K39"/>
+    <mergeCell ref="I40:K40"/>
+    <mergeCell ref="I22:K22"/>
     <mergeCell ref="I79:K79"/>
     <mergeCell ref="I61:K61"/>
     <mergeCell ref="I50:K50"/>
@@ -24407,27 +24411,40 @@
     <mergeCell ref="I58:K58"/>
     <mergeCell ref="I59:K59"/>
     <mergeCell ref="I60:K60"/>
-    <mergeCell ref="I49:K49"/>
-    <mergeCell ref="I6:K6"/>
-    <mergeCell ref="I7:K7"/>
-    <mergeCell ref="I8:K8"/>
-    <mergeCell ref="I9:K9"/>
-    <mergeCell ref="I16:K16"/>
-    <mergeCell ref="I17:K17"/>
-    <mergeCell ref="I18:K18"/>
-    <mergeCell ref="I21:K21"/>
-    <mergeCell ref="I38:K38"/>
-    <mergeCell ref="I39:K39"/>
-    <mergeCell ref="I40:K40"/>
-    <mergeCell ref="I22:K22"/>
-    <mergeCell ref="I120:K120"/>
-    <mergeCell ref="I121:K121"/>
-    <mergeCell ref="I122:K122"/>
-    <mergeCell ref="I115:K115"/>
-    <mergeCell ref="I116:K116"/>
-    <mergeCell ref="I117:K117"/>
-    <mergeCell ref="I118:K118"/>
-    <mergeCell ref="I119:K119"/>
+    <mergeCell ref="I62:K62"/>
+    <mergeCell ref="I63:K63"/>
+    <mergeCell ref="I64:K64"/>
+    <mergeCell ref="I66:K66"/>
+    <mergeCell ref="I78:K78"/>
+    <mergeCell ref="I108:K108"/>
+    <mergeCell ref="I109:K109"/>
+    <mergeCell ref="I98:K98"/>
+    <mergeCell ref="I99:K99"/>
+    <mergeCell ref="I100:K100"/>
+    <mergeCell ref="I101:K101"/>
+    <mergeCell ref="I102:K102"/>
+    <mergeCell ref="I103:K103"/>
+    <mergeCell ref="I104:K104"/>
+    <mergeCell ref="I105:K105"/>
+    <mergeCell ref="I106:K106"/>
+    <mergeCell ref="I107:K107"/>
+    <mergeCell ref="I97:K97"/>
+    <mergeCell ref="I80:K80"/>
+    <mergeCell ref="I81:K81"/>
+    <mergeCell ref="I82:K82"/>
+    <mergeCell ref="I83:K83"/>
+    <mergeCell ref="I84:K84"/>
+    <mergeCell ref="I86:K86"/>
+    <mergeCell ref="I89:K89"/>
+    <mergeCell ref="I94:K94"/>
+    <mergeCell ref="I95:K95"/>
+    <mergeCell ref="I96:K96"/>
+    <mergeCell ref="I85:K85"/>
+    <mergeCell ref="I110:K110"/>
+    <mergeCell ref="I111:K111"/>
+    <mergeCell ref="I112:K112"/>
+    <mergeCell ref="I113:K113"/>
+    <mergeCell ref="I114:K114"/>
   </mergeCells>
   <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -24444,9 +24461,9 @@
   </cols>
   <sheetData>
     <row r="1" spans="4:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="G1" s="168"/>
-      <c r="H1" s="168"/>
-      <c r="I1" s="168"/>
+      <c r="G1" s="169"/>
+      <c r="H1" s="169"/>
+      <c r="I1" s="169"/>
     </row>
     <row r="2" spans="4:12" ht="43.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="D2" s="24" t="s">
@@ -26754,11 +26771,11 @@
       <c r="W2" s="132"/>
       <c r="X2" s="132"/>
       <c r="Y2" s="132"/>
-      <c r="Z2" s="161" t="s">
+      <c r="Z2" s="153" t="s">
         <v>842</v>
       </c>
-      <c r="AA2" s="161"/>
-      <c r="AB2" s="161"/>
+      <c r="AA2" s="153"/>
+      <c r="AB2" s="153"/>
       <c r="AC2" s="132"/>
       <c r="AD2" s="132"/>
       <c r="AE2" s="132"/>
@@ -29180,33 +29197,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="6" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="170" t="s">
         <v>28</v>
       </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
-      <c r="H1" s="169"/>
-      <c r="I1" s="169"/>
-      <c r="J1" s="169"/>
-      <c r="K1" s="169"/>
-      <c r="L1" s="169"/>
-      <c r="M1" s="169"/>
-      <c r="N1" s="169"/>
-      <c r="O1" s="169"/>
-      <c r="P1" s="169"/>
-      <c r="Q1" s="169"/>
-      <c r="R1" s="169"/>
-      <c r="S1" s="169"/>
-      <c r="T1" s="169"/>
-      <c r="U1" s="169"/>
-      <c r="V1" s="169"/>
-      <c r="W1" s="169"/>
-      <c r="X1" s="169"/>
-      <c r="Y1" s="169"/>
+      <c r="B1" s="170"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="170"/>
+      <c r="G1" s="170"/>
+      <c r="H1" s="170"/>
+      <c r="I1" s="170"/>
+      <c r="J1" s="170"/>
+      <c r="K1" s="170"/>
+      <c r="L1" s="170"/>
+      <c r="M1" s="170"/>
+      <c r="N1" s="170"/>
+      <c r="O1" s="170"/>
+      <c r="P1" s="170"/>
+      <c r="Q1" s="170"/>
+      <c r="R1" s="170"/>
+      <c r="S1" s="170"/>
+      <c r="T1" s="170"/>
+      <c r="U1" s="170"/>
+      <c r="V1" s="170"/>
+      <c r="W1" s="170"/>
+      <c r="X1" s="170"/>
+      <c r="Y1" s="170"/>
     </row>
     <row r="2" spans="1:42" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
@@ -30368,33 +30385,33 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:42" s="6" customFormat="1" ht="30" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="169" t="s">
+      <c r="A1" s="170" t="s">
         <v>29</v>
       </c>
-      <c r="B1" s="169"/>
-      <c r="C1" s="169"/>
-      <c r="D1" s="169"/>
-      <c r="E1" s="169"/>
-      <c r="F1" s="169"/>
-      <c r="G1" s="169"/>
-      <c r="H1" s="169"/>
-      <c r="I1" s="169"/>
-      <c r="J1" s="169"/>
-      <c r="K1" s="169"/>
-      <c r="L1" s="169"/>
-      <c r="M1" s="169"/>
-      <c r="N1" s="169"/>
-      <c r="O1" s="169"/>
-      <c r="P1" s="169"/>
-      <c r="Q1" s="169"/>
-      <c r="R1" s="169"/>
-      <c r="S1" s="169"/>
-      <c r="T1" s="169"/>
-      <c r="U1" s="169"/>
-      <c r="V1" s="169"/>
-      <c r="W1" s="169"/>
-      <c r="X1" s="169"/>
-      <c r="Y1" s="169"/>
+      <c r="B1" s="170"/>
+      <c r="C1" s="170"/>
+      <c r="D1" s="170"/>
+      <c r="E1" s="170"/>
+      <c r="F1" s="170"/>
+      <c r="G1" s="170"/>
+      <c r="H1" s="170"/>
+      <c r="I1" s="170"/>
+      <c r="J1" s="170"/>
+      <c r="K1" s="170"/>
+      <c r="L1" s="170"/>
+      <c r="M1" s="170"/>
+      <c r="N1" s="170"/>
+      <c r="O1" s="170"/>
+      <c r="P1" s="170"/>
+      <c r="Q1" s="170"/>
+      <c r="R1" s="170"/>
+      <c r="S1" s="170"/>
+      <c r="T1" s="170"/>
+      <c r="U1" s="170"/>
+      <c r="V1" s="170"/>
+      <c r="W1" s="170"/>
+      <c r="X1" s="170"/>
+      <c r="Y1" s="170"/>
     </row>
     <row r="2" spans="1:42" s="6" customFormat="1" ht="30" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="10" t="s">
